--- a/Result/checksun_type/控制IC.xlsx
+++ b/Result/checksun_type/控制IC.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>37.21</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>38.22</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>38.41</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>38.41</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>915.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>1126.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>1126.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>1732.6</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>2097.92</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>2097.92</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-245.4020233382141</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>915</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>915.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>37.13</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>38.26</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>38.41</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>38.26</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>38.41</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>652.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>1621.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>1621.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>1774.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>2121.5</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>2121.5</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-219.5949860126452</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>652</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>652.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>37.23</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>38.36</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>38.42</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>38.36</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>38.42</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>952.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>1866.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>1866.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>1882.0</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>2150.8</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>2150.8</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-146.7065403328095</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>952</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>952.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>37.45</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>38.46</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>38.44</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>38.44</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>2025.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>2027.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>2027</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>2017.5</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>2158.84</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>2158.84</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-69.48352720687262</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>2025</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>2025.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>37.83</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>38.56</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>38.47</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>38.56</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>38.47</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>1087.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>1920.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>1920.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>2024.4</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>2161.76</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>2161.76</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-71.64766819814531</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>1087</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>1087.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>38.19</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>38.62</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>38.5</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>38.62</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>38.5</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>3393.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>2339.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>2339</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>2767.3</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>2159.12</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>2159.12</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>28.31954710711307</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>3393</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>3393.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>38.68</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>38.68</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>38.52</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>38.68</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>38.52</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>1875.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>1927.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>1927.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>2511.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>2157.84</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>2157.84</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-76.95298628205774</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>1875</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>1875.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>38.98999999999999</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>38.71</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>38.55</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>38.71</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>38.55</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>1755.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>1897.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>1897.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>2473.7</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>2149.54</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>2149.54</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-61.951141613657</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>1755</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>1755.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>39.14</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>38.54</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>38.54</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>1492.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>2008.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>2008</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>2476.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>2182.48</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>2182.48</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-25.4502513154539</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>1492</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>1492.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>39.33</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>38.66</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>38.54</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>38.66</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>38.54</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>3180.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>2128.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>2128.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>2407.1</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>2303.76</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>2303.76</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>55.78138665753113</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>3180</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>3180.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>39.52</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>38.61</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>38.56</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>38.61</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>38.56</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>1337.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>3195.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>3195.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>2342.5</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>2591.58</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>2591.58</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-11.02275147597402</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>1337</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1337.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>203.0</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>217.92</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>229.57</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>217.92</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>229.57</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>246990.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>261303.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>261303.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>360072.2</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>1087687.9</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>1087687.9</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-60756.27700912725</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>246990</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>246990.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>201.2</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>219.42</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>229.64</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>219.42</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>229.64</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>188584.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>277235.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>277235.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>364259.9</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>1109012.44</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>1109012.44</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-62901.108610934</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>188584</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>188584.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>200.9</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>221.0</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>229.9</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>221</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>229.9</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>266834.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>327128.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>327128.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>378625.9</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>1132112.48</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>1132112.48</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-57460.89987741027</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>266834</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>266834.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>203.5</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>223.02</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>230.31</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>223.02</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>230.31</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>328496.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>351582.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>351582.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>393659.8</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>1170503.62</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>1170503.62</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-56020.92669104022</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>328496</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>328496.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>206.5</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>225.2</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>230.45</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>225.2</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>230.45</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>275614.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>419383.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>419383</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>399217.9</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>1181679.14</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>1181679.14</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-58569.71761440305</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>275614</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>275614.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>209.8</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>227.1</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>230.35</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>227.1</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>230.35</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>326648.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>458840.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>458840.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>399885.8</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>1187183.2</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>1187183.2</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-54453.1433044069</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>326648</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>326648.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>214.9</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>229.28</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>230.34</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>229.28</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>230.34</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>438050.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>451284.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>451284.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>403006.7</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>1190565.96</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>1190565.96</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-52095.49631496938</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>438050</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>438050.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>219.1</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>230.98</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>230.29</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>230.98</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>230.29</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>389105.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>430123.4</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>430123.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>398138.1</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>1191948.4</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>1191948.4</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-58802.80431880965</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>389105</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>389105.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>222.5</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>232.15</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>229.96</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>232.15</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>229.96</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>667498.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>435737.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>435737</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>393344.8</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>1189336.42</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>1189336.42</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-61040.46559862403</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>667498</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>667498.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>225.1</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>233.28</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>229.57</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>233.28</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>229.57</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>472903.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>379052.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>379052.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>373683.5</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>1181965.28</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>1181965.28</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-91884.92936983652</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>472903</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>472903.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>226.8</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>233.52</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>229.07</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>233.52</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>229.07</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>288867.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>340930.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>340930.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>402140.3</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>1178670.4</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>1178670.4</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-111817.3801369317</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>288867</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>288867.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10463,11 +10331,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
           <t>2459</t>
@@ -10649,41 +10513,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT24" t="inlineStr">
         <is>
           <t>0</t>
@@ -10704,20 +10564,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>0</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>0</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10590,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>0</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10899,11 +10757,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
           <t>2458</t>
@@ -11085,41 +10939,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT25" t="inlineStr">
         <is>
           <t>0</t>
@@ -11140,20 +10990,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>0</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>0</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11016,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>0</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
